--- a/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R095451dd91b045af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1826d83030604b81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -71,6 +71,13 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -145,6 +152,23 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -534,6 +558,9 @@
           <x:t xml:space="preserve">triggerMaxActiveCount</x:t>
         </x:is>
       </x:c>
+      <x:c r="AC1" t="str">
+        <x:v>guaranteedFirstRoll</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="inlineStr">
@@ -676,6 +703,9 @@
           <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
+      <x:c r="AC2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="inlineStr">
@@ -818,6 +848,7 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
+      <x:c r="AC3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="inlineStr">
@@ -960,6 +991,9 @@
           <x:t xml:space="preserve">最大激活数量</x:t>
         </x:is>
       </x:c>
+      <x:c r="AC4" t="str">
+        <x:v>是否首次祝福必定出现</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="inlineStr">
@@ -1072,6 +1106,9 @@
       <x:c r="AB5" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC5" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="inlineStr">
@@ -1184,6 +1221,9 @@
       <x:c r="AB6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC6" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="inlineStr">
@@ -1296,6 +1336,9 @@
       <x:c r="AB7" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC7" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="inlineStr">
@@ -1408,6 +1451,9 @@
       <x:c r="AB8" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC8" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="inlineStr">
@@ -1520,6 +1566,9 @@
       <x:c r="AB9" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC9" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="inlineStr">
@@ -1632,6 +1681,9 @@
       <x:c r="AB10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC10" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="inlineStr">
@@ -1740,6 +1792,9 @@
       <x:c r="AB11" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC11" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="3" t="inlineStr">
@@ -1852,6 +1907,9 @@
       <x:c r="AB12" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AC12" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="3" t="inlineStr">
@@ -1963,6 +2021,92 @@
       </x:c>
       <x:c r="AB13" s="3" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC13" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="n">
+        <x:v>1104</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>双主武器</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>获得另一把主武器</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>WeaponStat</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14"/>
+      <x:c r="N14" t="str">
+        <x:v>Blessing_ExtraPrimaryWeapon</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="P14" t="str">
+        <x:v>GrantMissingPrimaryWeapon</x:v>
+      </x:c>
+      <x:c r="Q14" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U14" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X14"/>
+      <x:c r="Y14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC14" s="6" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1826d83030604b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91a9641ea86940b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -561,6 +561,12 @@
       <x:c r="AC1" t="str">
         <x:v>guaranteedFirstRoll</x:v>
       </x:c>
+      <x:c r="AD1" t="str">
+        <x:v>triggerAudioKey</x:v>
+      </x:c>
+      <x:c r="AE1" t="str">
+        <x:v>guaranteedUntilSelectedFromRoll</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="inlineStr">
@@ -706,6 +712,12 @@
       <x:c r="AC2" t="str">
         <x:v>bool</x:v>
       </x:c>
+      <x:c r="AD2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AE2" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="inlineStr">
@@ -849,6 +861,8 @@
         </x:is>
       </x:c>
       <x:c r="AC3"/>
+      <x:c r="AD3"/>
+      <x:c r="AE3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="inlineStr">
@@ -994,6 +1008,12 @@
       <x:c r="AC4" t="str">
         <x:v>是否首次祝福必定出现</x:v>
       </x:c>
+      <x:c r="AD4" t="str">
+        <x:v>触发音效key</x:v>
+      </x:c>
+      <x:c r="AE4" t="str">
+        <x:v>从第几次抽取开始持续保底到选中 0关闭</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="inlineStr">
@@ -1109,6 +1129,10 @@
       <x:c r="AC5" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AD5"/>
+      <x:c r="AE5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="inlineStr">
@@ -1151,7 +1175,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="3" t="n">
-        <x:v>90</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K6" s="3" t="n">
         <x:v>5</x:v>
@@ -1222,6 +1246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC6" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD6"/>
+      <x:c r="AE6" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1266,7 +1294,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="3" t="n">
-        <x:v>80</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K7" s="3" t="n">
         <x:v>5</x:v>
@@ -1337,6 +1365,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC7" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD7"/>
+      <x:c r="AE7" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1381,7 +1413,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="3" t="n">
-        <x:v>100</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K8" s="3" t="n">
         <x:v>5</x:v>
@@ -1452,6 +1484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC8" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD8"/>
+      <x:c r="AE8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1569,6 +1605,10 @@
       <x:c r="AC9" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AD9"/>
+      <x:c r="AE9" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="inlineStr">
@@ -1684,6 +1724,10 @@
       <x:c r="AC10" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AD10"/>
+      <x:c r="AE10" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="inlineStr">
@@ -1726,7 +1770,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="3" t="n">
-        <x:v>90</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K11" s="3" t="n">
         <x:v>5</x:v>
@@ -1793,6 +1837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC11" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD11"/>
+      <x:c r="AE11" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1910,6 +1958,10 @@
       <x:c r="AC12" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="AD12"/>
+      <x:c r="AE12" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="3" t="inlineStr">
@@ -2023,6 +2075,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC13" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD13"/>
+      <x:c r="AE13" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2108,6 +2164,619 @@
       <x:c r="AC14" s="6" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AD14"/>
+      <x:c r="AE14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15" t="n">
+        <x:v>1401</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>爆炸子弹</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>枪械击杀敌人时有80%概率引发爆炸</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15"/>
+      <x:c r="N15" t="str">
+        <x:v>Blessing_ExplosiveBullet</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="P15"/>
+      <x:c r="Q15"/>
+      <x:c r="R15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U15" t="str">
+        <x:v>OnKillEnemy</x:v>
+      </x:c>
+      <x:c r="V15" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="W15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X15" t="str">
+        <x:v>Onomatopoeia_Bam Variant</x:v>
+      </x:c>
+      <x:c r="Y15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="Z15" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AA15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC15" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD15" t="str">
+        <x:v>SkillBoom</x:v>
+      </x:c>
+      <x:c r="AE15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>轻盈步伐</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>跳跃高度 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>PlayerStat</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K16" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16"/>
+      <x:c r="N16" t="str">
+        <x:v>Blessing_JumpHeight</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P16" t="str">
+        <x:v>JumpHeight</x:v>
+      </x:c>
+      <x:c r="Q16" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R16" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="S16" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="T16" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="U16" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X16"/>
+      <x:c r="Y16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC16" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD16"/>
+      <x:c r="AE16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17" t="n">
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>全武装强化</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>本局所有已携带武器额外提升 {0} 级</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>WeaponStat</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K17" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17"/>
+      <x:c r="N17" t="str">
+        <x:v>Blessing_AllWeaponsUpgrade</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="P17" t="str">
+        <x:v>WeaponUpgradeLevel</x:v>
+      </x:c>
+      <x:c r="Q17" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X17"/>
+      <x:c r="Y17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC17" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD17"/>
+      <x:c r="AE17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="n">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>肾上腺强化</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>狂暴持续时间 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>PlayerStat</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K18" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18"/>
+      <x:c r="N18" t="str">
+        <x:v>Blessing_BerserkDuration</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>BerserkDuration</x:v>
+      </x:c>
+      <x:c r="Q18" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R18" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="S18" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="T18" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="U18" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18"/>
+      <x:c r="Y18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC18" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD18"/>
+      <x:c r="AE18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="n">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>爆破专精</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>炸弹和敌人爆炸伤害 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19"/>
+      <x:c r="N19" t="str">
+        <x:v>Blessing_ExplosionDamage</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
+        <x:v>ExplosionDamage</x:v>
+      </x:c>
+      <x:c r="Q19" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="S19" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="T19" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="U19" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19"/>
+      <x:c r="Y19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC19" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD19"/>
+      <x:c r="AE19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20" t="n">
+        <x:v>1302</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>弹药搜刮</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>弹药道具获取量 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Economy</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20"/>
+      <x:c r="N20" t="str">
+        <x:v>Blessing_PickupAmmoGain</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>PickupAmmoGain</x:v>
+      </x:c>
+      <x:c r="Q20" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R20" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="S20" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="T20" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="U20" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X20"/>
+      <x:c r="Y20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC20" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD20"/>
+      <x:c r="AE20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21" t="n">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>医疗增效</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>医疗道具恢复量 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>PlayerStat</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K21" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21"/>
+      <x:c r="N21" t="str">
+        <x:v>Blessing_PickupHealing</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>PickupHealing</x:v>
+      </x:c>
+      <x:c r="Q21" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R21" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="S21" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="T21" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="U21" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X21"/>
+      <x:c r="Y21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC21" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD21"/>
+      <x:c r="AE21" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
+++ b/FPSDemo/MiniTemplate/Datas/#blessing.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91a9641ea86940b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raae62aa1e0a141c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1175,7 +1175,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J6" s="3" t="n">
-        <x:v>170</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K6" s="3" t="n">
         <x:v>5</x:v>
@@ -1413,10 +1413,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="3" t="n">
-        <x:v>180</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K8" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="3" t="n">
         <x:v>0</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="K9" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="3" t="n">
         <x:v>0</x:v>
@@ -1770,7 +1770,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="3" t="n">
-        <x:v>170</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K11" s="3" t="n">
         <x:v>5</x:v>
@@ -2283,7 +2283,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J16" t="n">
-        <x:v>160</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K16" t="n">
         <x:v>5</x:v>
@@ -2370,10 +2370,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" t="n">
-        <x:v>160</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K17" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L17" t="n">
         <x:v>0</x:v>
@@ -2457,7 +2457,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J18" t="n">
-        <x:v>190</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K18" t="n">
         <x:v>5</x:v>
@@ -2544,10 +2544,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J19" t="n">
-        <x:v>200</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K19" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L19" t="n">
         <x:v>0</x:v>
@@ -2631,7 +2631,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J20" t="n">
-        <x:v>190</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K20" t="n">
         <x:v>5</x:v>
@@ -2718,7 +2718,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J21" t="n">
-        <x:v>190</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K21" t="n">
         <x:v>5</x:v>
@@ -2775,6 +2775,872 @@
       </x:c>
       <x:c r="AD21"/>
       <x:c r="AE21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22" t="n">
+        <x:v>1106</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>急速扳机</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>所有武器射击速度 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>WeaponStat</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22"/>
+      <x:c r="N22" t="str">
+        <x:v>Blessing_FireRate</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>WeaponFireRate</x:v>
+      </x:c>
+      <x:c r="Q22" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R22" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="S22" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="T22" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="U22" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X22"/>
+      <x:c r="Y22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC22" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD22"/>
+      <x:c r="AE22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23" t="n">
+        <x:v>1107</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>战术换弹</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>所有武器换弹速度 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>WeaponStat</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23"/>
+      <x:c r="N23" t="str">
+        <x:v>Blessing_ReloadSpeed</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>WeaponReloadSpeed</x:v>
+      </x:c>
+      <x:c r="Q23" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R23" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="S23" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="T23" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="U23" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X23"/>
+      <x:c r="Y23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC23" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD23"/>
+      <x:c r="AE23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24" t="n">
+        <x:v>1303</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>以战养战</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>每次击杀使所有已携带武器备弹 +{value}</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Economy</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24"/>
+      <x:c r="N24" t="str">
+        <x:v>Blessing_KillAmmo</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P24" t="str">
+        <x:v>KillAmmoRestore</x:v>
+      </x:c>
+      <x:c r="Q24" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U24" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X24"/>
+      <x:c r="Y24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC24" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD24"/>
+      <x:c r="AE24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25" t="n">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>血战续航</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>每次击杀恢复 {value} 点生命</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>PlayerStat</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="K25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25"/>
+      <x:c r="N25" t="str">
+        <x:v>Blessing_KillHealing</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>KillHealthRestore</x:v>
+      </x:c>
+      <x:c r="Q25" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T25" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U25" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X25"/>
+      <x:c r="Y25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC25" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD25"/>
+      <x:c r="AE25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26" t="n">
+        <x:v>1108</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>深度弹仓</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>所有武器备弹上限 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>WeaponStat</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="K26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26"/>
+      <x:c r="N26" t="str">
+        <x:v>Blessing_ReserveAmmo</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>AllWeapons</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>WeaponReserveAmmo</x:v>
+      </x:c>
+      <x:c r="Q26" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R26" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="S26" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="T26" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="U26" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X26"/>
+      <x:c r="Y26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC26" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD26"/>
+      <x:c r="AE26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27" t="n">
+        <x:v>1203</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>技能增幅</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>所有技能伤害 +{value:P0}</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>SkillStat</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27"/>
+      <x:c r="N27" t="str">
+        <x:v>Blessing_SkillDamage</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>SkillDamage</x:v>
+      </x:c>
+      <x:c r="Q27" t="str">
+        <x:v>PercentAdd</x:v>
+      </x:c>
+      <x:c r="R27" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="S27" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="T27" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="U27" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="V27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X27"/>
+      <x:c r="Y27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC27" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD27"/>
+      <x:c r="AE27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28" t="n">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>杀戮狂热</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>击杀敌人每层增加 12% 狂暴触发概率，最高 30%；狂暴期间不会重复触发</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="K28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28"/>
+      <x:c r="N28" t="str">
+        <x:v>Blessing_KillBerserk</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>KillBerserkDuration</x:v>
+      </x:c>
+      <x:c r="Q28" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R28" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="S28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="U28" t="str">
+        <x:v>OnKillEnemy</x:v>
+      </x:c>
+      <x:c r="V28" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="W28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X28" t="str">
+        <x:v>Pickup_Berserk_SpeedLines</x:v>
+      </x:c>
+      <x:c r="Y28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC28" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD28"/>
+      <x:c r="AE28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29" t="n">
+        <x:v>1404</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>空投炸弹</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>枪械命中有 60% 概率从侧上方飞来一枚炸弹</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29"/>
+      <x:c r="N29" t="str">
+        <x:v>Blessing_AirBomb</x:v>
+      </x:c>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
+      <x:c r="Q29"/>
+      <x:c r="R29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U29" t="str">
+        <x:v>OnHitEnemy</x:v>
+      </x:c>
+      <x:c r="V29" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="W29" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="X29" t="str">
+        <x:v>bomb</x:v>
+      </x:c>
+      <x:c r="Y29" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="Z29" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AA29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB29" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AC29" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD29"/>
+      <x:c r="AE29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30" t="n">
+        <x:v>1405</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>越战越勇</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>击杀敌人每层有 10% 概率随机提升本局基础属性，三层最高 30%</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30"/>
+      <x:c r="N30" t="str">
+        <x:v>Blessing_KillGrowth</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>KillRandomBaseStat</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="R30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S30" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="T30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U30" t="str">
+        <x:v>OnKillEnemy</x:v>
+      </x:c>
+      <x:c r="V30" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="W30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X30" t="str">
+        <x:v>RandomBaseStat</x:v>
+      </x:c>
+      <x:c r="Y30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC30" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD30"/>
+      <x:c r="AE30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31" t="n">
+        <x:v>1406</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>战利品猎手</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>击杀敌人有 8% 概率在尸体附近掉落随机道具，狂暴道具较为稀有</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>GameplayTrigger</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31"/>
+      <x:c r="N31" t="str">
+        <x:v>Blessing_KillPickup</x:v>
+      </x:c>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
+      <x:c r="Q31"/>
+      <x:c r="R31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U31" t="str">
+        <x:v>OnKillEnemy</x:v>
+      </x:c>
+      <x:c r="V31" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="W31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X31" t="str">
+        <x:v>RandomPickupNoBerserk</x:v>
+      </x:c>
+      <x:c r="Y31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AC31" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD31"/>
+      <x:c r="AE31" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
